--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0001T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0001T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>62.3483207483343</v>
+        <v>10.13160212160432</v>
       </c>
       <c r="D2" t="n">
-        <v>84.16116896131579</v>
+        <v>13.67618995621382</v>
       </c>
       <c r="E2" t="n">
-        <v>12.09957390136603</v>
+        <v>1.96618075897198</v>
       </c>
       <c r="F2" t="n">
-        <v>15.38019138901857</v>
+        <v>2.499281100715517</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>38.14917294560225</v>
+        <v>6.199240603660365</v>
       </c>
       <c r="D3" t="n">
-        <v>53.40078618327866</v>
+        <v>8.677627754782783</v>
       </c>
       <c r="E3" t="n">
-        <v>12.09957390136603</v>
+        <v>1.96618075897198</v>
       </c>
       <c r="F3" t="n">
-        <v>15.38019138901857</v>
+        <v>2.499281100715517</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
